--- a/be/tools/mindbody/transform/fixtures/reports/Clients/17 Schedule at a Glance/17 Schedule at a Glance - 2090.xlsx
+++ b/be/tools/mindbody/transform/fixtures/reports/Clients/17 Schedule at a Glance/17 Schedule at a Glance - 2090.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -61,6 +61,9 @@
     <t xml:space="preserve">Membership</t>
   </si>
   <si>
+    <t xml:space="preserve">Appointment Notes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hatha</t>
   </si>
   <si>
@@ -347,6 +350,33 @@
   </si>
   <si>
     <t xml:space="preserve">Client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal Training / PT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner, Olive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Hall </t>
+  </si>
+  <si>
+    <t xml:space="preserve">林, Mei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100000008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivy Instructor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Left knee: no deep lunges</t>
   </si>
 </sst>
 </file>
@@ -406,6 +436,9 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -418,22 +451,22 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -442,16 +475,16 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -465,22 +498,22 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -489,16 +522,16 @@
         <v>6</v>
       </c>
       <c r="M3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -512,22 +545,22 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -536,16 +569,16 @@
         <v>6</v>
       </c>
       <c r="M4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -559,22 +592,22 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -583,16 +616,16 @@
         <v>99950</v>
       </c>
       <c r="N5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -606,22 +639,22 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -630,13 +663,13 @@
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -650,22 +683,22 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -674,13 +707,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -694,19 +727,19 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -715,16 +748,16 @@
         <v>7</v>
       </c>
       <c r="N8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -738,22 +771,22 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -762,16 +795,16 @@
         <v>6</v>
       </c>
       <c r="M9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -785,22 +818,22 @@
         <v>0.375</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -809,13 +842,13 @@
         <v>99950</v>
       </c>
       <c r="N10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -829,22 +862,22 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -853,16 +886,60 @@
         <v>6</v>
       </c>
       <c r="M11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P11" t="s">
-        <v>112</v>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>46266</v>
+      </c>
+      <c r="B12">
+        <v>0.375</v>
+      </c>
+      <c r="C12">
+        <v>0.4375</v>
+      </c>
+      <c r="D12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G12" t="s">
+        <v>116</v>
+      </c>
+      <c r="I12" t="s">
+        <v>117</v>
+      </c>
+      <c r="J12" t="s">
+        <v>118</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>7</v>
+      </c>
+      <c r="N12" t="s">
+        <v>119</v>
+      </c>
+      <c r="O12" t="s">
+        <v>120</v>
+      </c>
+      <c r="P12" t="s">
+        <v>121</v>
+      </c>
+      <c r="R12" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
